--- a/keywordCard.xlsx
+++ b/keywordCard.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\02_Dev\triw\triw-app\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD1CE486-74BF-49D9-BF5D-670BE8B8B9EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="12400" yWindow="5830" windowWidth="28800" windowHeight="14160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,14 +24,264 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="75">
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>label</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>promptText</t>
+  </si>
+  <si>
+    <t>rain</t>
+  </si>
+  <si>
+    <t>雨</t>
+  </si>
+  <si>
+    <t>weather</t>
+  </si>
+  <si>
+    <t>雨は、湿度、反射する街灯、窓の外を眺める感覚、孤独、少し閉じた空気として扱う。曲名にRainや雨が入っている必要はない。</t>
+  </si>
+  <si>
+    <t>summer</t>
+  </si>
+  <si>
+    <t>夏</t>
+  </si>
+  <si>
+    <t>season</t>
+  </si>
+  <si>
+    <t>夏は、強い光、湿気、夜風、開放感、少し浮ついた気分、終わりが近づく切なさとして扱う。</t>
+  </si>
+  <si>
+    <t>winter</t>
+  </si>
+  <si>
+    <t>冬</t>
+  </si>
+  <si>
+    <t>冬は、冷たい空気、乾いた光、静けさ、距離感、内省、厚着した身体感覚として扱う。</t>
+  </si>
+  <si>
+    <t>lateNight</t>
+  </si>
+  <si>
+    <t>深夜</t>
+  </si>
+  <si>
+    <t>time</t>
+  </si>
+  <si>
+    <t>深夜は、人の少なさ、静けさ、眠らない街、ひとりの時間、少し現実から離れた感覚として扱う。歌詞の内容だけでなく、音数の少なさ、空白、小さな音量でも成立する感じ、近い声、抑えたビート、過度に盛り上がらない曲調、ヘッドホンで聴く距離感を重視する。</t>
+  </si>
+  <si>
+    <t>evening</t>
+  </si>
+  <si>
+    <t>夕方</t>
+  </si>
+  <si>
+    <t>夕方は、一日の終わり、斜めの光、帰り道、少し寂しい高揚、これから夜に向かう感じとして扱う。</t>
+  </si>
+  <si>
+    <t>drive</t>
+  </si>
+  <si>
+    <t>ドライブ</t>
+  </si>
+  <si>
+    <t>action</t>
+  </si>
+  <si>
+    <t>ドライブは、移動感、車窓、流れる景色、速度感、ひとりの時間、目的地へ向かう高揚として扱う。車や道を直接歌った曲に限定しない。</t>
+  </si>
+  <si>
+    <t>walk</t>
+  </si>
+  <si>
+    <t>散歩</t>
+  </si>
+  <si>
+    <t>散歩は、歩くテンポ、街の観察、寄り道、軽い内省、生活の中の移動として扱う。</t>
+  </si>
+  <si>
+    <t>highway</t>
+  </si>
+  <si>
+    <t>高速道路</t>
+  </si>
+  <si>
+    <t>place</t>
+  </si>
+  <si>
+    <t>高速道路は、夜の移動、一定の速度、遠くの灯り、逃避、目的地に向かう緊張感として扱う。</t>
+  </si>
+  <si>
+    <t>seaside</t>
+  </si>
+  <si>
+    <t>海沿い</t>
+  </si>
+  <si>
+    <t>海沿いは、開けた視界、風、水平線、潮の匂い、少し遠くへ来た感じとして扱う。</t>
+  </si>
+  <si>
+    <t>room</t>
+  </si>
+  <si>
+    <t>部屋</t>
+  </si>
+  <si>
+    <t>部屋は、室内の静けさ、個人的な時間、閉じた安心感、外の世界との距離として扱う。</t>
+  </si>
+  <si>
+    <t>loneliness</t>
+  </si>
+  <si>
+    <t>孤独</t>
+  </si>
+  <si>
+    <t>emotion</t>
+  </si>
+  <si>
+    <t>孤独は、悲しみだけでなく、ひとりでいる自由、距離感、静かな集中、自分だけの時間として扱う。</t>
+  </si>
+  <si>
+    <t>happiness</t>
+  </si>
+  <si>
+    <t>多幸感</t>
+  </si>
+  <si>
+    <t>多幸感は、祝祭感、軽さ、身体が浮く感じ、明るい高揚、理由のないうれしさとして扱う。</t>
+  </si>
+  <si>
+    <t>bittersweet</t>
+  </si>
+  <si>
+    <t>切なさ</t>
+  </si>
+  <si>
+    <t>切なさは、甘さと寂しさが混ざった感情、過ぎていく時間、思い出、少しだけ胸が痛む感じとして扱う。</t>
+  </si>
+  <si>
+    <t>escape</t>
+  </si>
+  <si>
+    <t>逃避</t>
+  </si>
+  <si>
+    <t>逃避は、日常から離れたい気分、どこかへ行きたい衝動、現実との距離、少し危うい自由として扱う。</t>
+  </si>
+  <si>
+    <t>alternative</t>
+  </si>
+  <si>
+    <t>オルタナ</t>
+  </si>
+  <si>
+    <t>culture</t>
+  </si>
+  <si>
+    <t>オルタナは、主流から少し外れた感覚、ひねりのあるメロディ、歪み、内省、インディー／ポストパンク／シューゲイズ的な質感として扱う。</t>
+  </si>
+  <si>
+    <t>lofi</t>
+  </si>
+  <si>
+    <t>ローファイ</t>
+  </si>
+  <si>
+    <t>texture</t>
+  </si>
+  <si>
+    <t>ローファイは、ざらつき、手触り、録音の粗さ、親密さ、過度に磨かれていない質感として扱う。</t>
+  </si>
+  <si>
+    <t>floating</t>
+  </si>
+  <si>
+    <t>浮遊感</t>
+  </si>
+  <si>
+    <t>浮遊感は、重力が薄い感じ、ぼんやりした輪郭、夢の中のような距離感、空間的な広がりとして扱う。</t>
+  </si>
+  <si>
+    <t>electronic</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>電子音</t>
+    <rPh sb="2" eb="3">
+      <t>オン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>電子音感は、シンセサイザー、打ち込み、無機的な反復、人工的な質感、機械的なビートとして扱う。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>jazz-like</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ジャズ感</t>
+    <rPh sb="3" eb="4">
+      <t>カン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ジャズ感は、コードの複雑さ、演奏の揺らぎ、夜の空気、即興感、落ち着いたグルーヴ、演奏者同士の会話感として扱う。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>mainstream</t>
+  </si>
+  <si>
+    <t>王道性</t>
+  </si>
+  <si>
+    <t>world</t>
+  </si>
+  <si>
+    <t>非英米中心</t>
+  </si>
+  <si>
+    <t>王道性は、多くの人に開かれたメロディ、洗練された構成、強いフック、広く共有される感情、大衆性として扱う。単なる現在の人気ではなく、『みんなが自然に受け入れやすい感覚』を重視する。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>非英米中心は、英米ポップス中心の感覚から少し離れた文化圏、言語感覚、リズム、土着性、地域ごとの空気感として扱う。特定ジャンル名だけでなく、多言語性や地域固有のグルーヴ、楽器感、空気感も重視する。</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -49,11 +305,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -330,10 +589,321 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D23"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" t="s">
+        <v>49</v>
+      </c>
+      <c r="B15" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" t="s">
+        <v>41</v>
+      </c>
+      <c r="D15" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" t="s">
+        <v>52</v>
+      </c>
+      <c r="B16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C16" t="s">
+        <v>54</v>
+      </c>
+      <c r="D16" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" t="s">
+        <v>54</v>
+      </c>
+      <c r="D17" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C18" t="s">
+        <v>54</v>
+      </c>
+      <c r="D18" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" t="s">
+        <v>56</v>
+      </c>
+      <c r="B20" t="s">
+        <v>57</v>
+      </c>
+      <c r="C20" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" t="s">
+        <v>60</v>
+      </c>
+      <c r="B21" t="s">
+        <v>61</v>
+      </c>
+      <c r="C21" t="s">
+        <v>58</v>
+      </c>
+      <c r="D21" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" t="s">
+        <v>63</v>
+      </c>
+      <c r="B22" t="s">
+        <v>64</v>
+      </c>
+      <c r="C22" t="s">
+        <v>58</v>
+      </c>
+      <c r="D22" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" t="s">
+        <v>66</v>
+      </c>
+      <c r="B23" t="s">
+        <v>67</v>
+      </c>
+      <c r="C23" t="s">
+        <v>58</v>
+      </c>
+      <c r="D23" t="s">
+        <v>68</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" copies="3" r:id="rId1"/>
 </worksheet>
 </file>